--- a/data/gaming/manualdata_gaming/_manualdata_master_gaming.xlsx
+++ b/data/gaming/manualdata_gaming/_manualdata_master_gaming.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\notebookpick\data\manualdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\notebookpick\data\gaming\manualdata_gaming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71E823CC-1E9A-4552-8DA7-AC439CEE65A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC5BF3EB-99C9-4B36-B3DD-320AC9C2D4FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{52B35C0C-4AC1-4CD7-A119-F59BBD510595}"/>
   </bookViews>
@@ -645,9 +645,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpadx9/thinkpad-x9-aura-edition-15-inch-intel/21q6cto1wwkr3</t>
-  </si>
-  <si>
     <t>lenovo</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -668,9 +665,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpade/thinkpad-e14-gen-7-14-inch-intel-laptop/21u2cto1wwkr2</t>
-  </si>
-  <si>
     <t>ips</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -679,9 +673,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpade/lenovo-thinkpad-e16-gen-3-16-inch-intel/22aycto1wwkr1</t>
-  </si>
-  <si>
     <t>씽크패드 x13, u5 225H</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -690,9 +681,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpadx/thinkpad-x13-gen-6-13-inch-intel/21rkcto1wwkr3</t>
-  </si>
-  <si>
     <t>https://item.gmarket.co.kr/Item?goodscode=4623684498</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -822,6 +810,22 @@
   </si>
   <si>
     <t>not_selling</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpadx/thinkpad-x13-gen-6-13-inch-intel/21rkcto1wwkr3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpade/lenovo-thinkpad-e16-gen-3-16-inch-intel/22aycto1wwkr1</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpadx9/thinkpad-x9-aura-edition-15-inch-intel/21q6cto1wwkr3</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.lenovo.com/kr/ko/p/laptops/thinkpad/thinkpade/thinkpad-e14-gen-7-14-inch-intel-laptop/21u2cto1wwkr2</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1844,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -1868,7 +1872,7 @@
         <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="Q1" t="s">
         <v>14</v>
@@ -1918,13 +1922,13 @@
         <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1943,13 +1947,13 @@
         <v>-7.1428571428571423</v>
       </c>
       <c r="L2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M2">
         <v>16</v>
       </c>
       <c r="N2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O2">
         <v>512</v>
@@ -1970,7 +1974,7 @@
         <v>75</v>
       </c>
       <c r="U2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="V2">
         <v>7</v>
@@ -1979,7 +1983,7 @@
         <v>9.5</v>
       </c>
       <c r="X2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Z2">
         <f t="shared" ref="Z2:Z33" si="0">T2/W2</f>
@@ -2007,7 +2011,7 @@
         <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
         <v>120</v>
@@ -2071,7 +2075,7 @@
         <v>11</v>
       </c>
       <c r="X3" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Z3">
         <f t="shared" si="0"/>
@@ -2099,7 +2103,7 @@
         <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C4" t="s">
         <v>120</v>
@@ -2160,7 +2164,7 @@
         <v>10</v>
       </c>
       <c r="X4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Z4">
         <f t="shared" si="0"/>
@@ -2188,7 +2192,7 @@
         <v>67</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C5" t="s">
         <v>120</v>
@@ -2200,7 +2204,7 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -2252,7 +2256,7 @@
         <v>7.25</v>
       </c>
       <c r="X5" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
@@ -2280,19 +2284,19 @@
         <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" t="s">
         <v>219</v>
       </c>
-      <c r="D6" t="s">
-        <v>223</v>
-      </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -2308,13 +2312,13 @@
         <v>-7.6923076923076925</v>
       </c>
       <c r="L6" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="M6">
         <v>16</v>
       </c>
       <c r="N6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O6">
         <v>512</v>
@@ -2335,7 +2339,7 @@
         <v>100</v>
       </c>
       <c r="U6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="V6">
         <v>7</v>
@@ -2344,7 +2348,7 @@
         <v>10.25</v>
       </c>
       <c r="X6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Z6">
         <f t="shared" si="0"/>
@@ -2372,13 +2376,13 @@
         <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -2397,13 +2401,13 @@
         <v>8.5714285714285712</v>
       </c>
       <c r="L7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="M7">
         <v>16</v>
       </c>
       <c r="N7" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O7">
         <v>256</v>
@@ -2424,7 +2428,7 @@
         <v>54</v>
       </c>
       <c r="U7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V7">
         <v>3</v>
@@ -2433,7 +2437,7 @@
         <v>10.25</v>
       </c>
       <c r="X7" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Z7">
         <f t="shared" si="0"/>
@@ -2461,13 +2465,13 @@
         <v>79</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D8" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2486,13 +2490,13 @@
         <v>12</v>
       </c>
       <c r="L8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M8">
         <v>16</v>
       </c>
       <c r="N8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O8">
         <v>256</v>
@@ -2513,7 +2517,7 @@
         <v>76</v>
       </c>
       <c r="U8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -2522,7 +2526,7 @@
         <v>7.5</v>
       </c>
       <c r="X8" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Z8">
         <f t="shared" si="0"/>
@@ -2550,13 +2554,13 @@
         <v>78</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -2575,13 +2579,13 @@
         <v>9.0909090909090917</v>
       </c>
       <c r="L9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M9">
         <v>16</v>
       </c>
       <c r="N9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O9">
         <v>256</v>
@@ -2602,7 +2606,7 @@
         <v>63</v>
       </c>
       <c r="U9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -2611,7 +2615,7 @@
         <v>6.75</v>
       </c>
       <c r="X9" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
@@ -2638,14 +2642,14 @@
       <c r="A10">
         <v>64</v>
       </c>
-      <c r="B10" t="s">
-        <v>215</v>
+      <c r="B10" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D10" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -2667,13 +2671,13 @@
         <v>6.25</v>
       </c>
       <c r="L10" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="M10">
         <v>32</v>
       </c>
       <c r="N10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O10">
         <v>256</v>
@@ -2694,7 +2698,7 @@
         <v>55</v>
       </c>
       <c r="U10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -2703,7 +2707,7 @@
         <v>6</v>
       </c>
       <c r="X10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z10">
         <f t="shared" si="0"/>
@@ -2730,14 +2734,14 @@
       <c r="A11">
         <v>63</v>
       </c>
-      <c r="B11" t="s">
-        <v>212</v>
+      <c r="B11" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="C11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D11" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -2759,13 +2763,13 @@
         <v>-6.4</v>
       </c>
       <c r="L11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="M11">
         <v>16</v>
       </c>
       <c r="N11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O11">
         <v>256</v>
@@ -2786,7 +2790,7 @@
         <v>64</v>
       </c>
       <c r="U11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -2795,7 +2799,7 @@
         <v>7.5</v>
       </c>
       <c r="X11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
@@ -2822,14 +2826,14 @@
       <c r="A12">
         <v>61</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="C12" t="s">
         <v>203</v>
       </c>
-      <c r="C12" t="s">
-        <v>204</v>
-      </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -2851,13 +2855,13 @@
         <v>-5.1282051282051277</v>
       </c>
       <c r="L12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M12">
         <v>32</v>
       </c>
       <c r="N12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O12">
         <v>512</v>
@@ -2878,7 +2882,7 @@
         <v>80</v>
       </c>
       <c r="U12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -2887,7 +2891,7 @@
         <v>7.5</v>
       </c>
       <c r="X12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z12">
         <f t="shared" si="0"/>
@@ -2914,14 +2918,14 @@
       <c r="A13">
         <v>62</v>
       </c>
-      <c r="B13" t="s">
-        <v>209</v>
+      <c r="B13" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C13" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -2943,13 +2947,13 @@
         <v>-1.4814814814814816</v>
       </c>
       <c r="L13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="M13">
         <v>32</v>
       </c>
       <c r="N13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="O13">
         <v>512</v>
@@ -2970,7 +2974,7 @@
         <v>64</v>
       </c>
       <c r="U13" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -2979,7 +2983,7 @@
         <v>6.75</v>
       </c>
       <c r="X13" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Z13">
         <f t="shared" si="0"/>
@@ -5028,7 +5032,7 @@
         <v/>
       </c>
       <c r="L37" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="M37">
         <v>16</v>
@@ -6130,7 +6134,7 @@
         <v>120</v>
       </c>
       <c r="D50" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -6146,7 +6150,7 @@
         <v/>
       </c>
       <c r="L50" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M50">
         <v>32</v>
@@ -6216,7 +6220,7 @@
         <v>120</v>
       </c>
       <c r="D51" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="E51">
         <v>1</v>
@@ -6232,7 +6236,7 @@
         <v/>
       </c>
       <c r="L51" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="M51">
         <v>16</v>
@@ -7610,7 +7614,7 @@
         <v>120</v>
       </c>
       <c r="D67" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E67">
         <v>1</v>
@@ -7629,7 +7633,7 @@
         <v/>
       </c>
       <c r="L67" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="M67">
         <v>32</v>
@@ -7699,7 +7703,7 @@
         <v>120</v>
       </c>
       <c r="D68" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="E68">
         <v>2</v>
@@ -7718,7 +7722,7 @@
         <v/>
       </c>
       <c r="L68" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="M68">
         <v>32</v>
@@ -8826,8 +8830,12 @@
     <hyperlink ref="B7" r:id="rId3" xr:uid="{C68D053D-6A31-45F0-9494-12AE26E861B2}"/>
     <hyperlink ref="B9" r:id="rId4" xr:uid="{836DAA7E-3698-46B3-956C-2D7F97CE46FB}"/>
     <hyperlink ref="B8" r:id="rId5" xr:uid="{637EE4E2-122C-4B62-A3AA-BF8885E38863}"/>
+    <hyperlink ref="B10" r:id="rId6" xr:uid="{0AFB4538-D3F3-4530-9F97-BB9A3550E239}"/>
+    <hyperlink ref="B11" r:id="rId7" xr:uid="{6FFD2A4E-81F8-4BA6-B857-D094B01A02B3}"/>
+    <hyperlink ref="B12" r:id="rId8" xr:uid="{B77014D3-B689-4DD3-8959-BA8A15EB5D35}"/>
+    <hyperlink ref="B13" r:id="rId9" xr:uid="{82D51608-DA8E-45EE-A019-1272344E3EAD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
 </worksheet>
 </file>